--- a/data/mgmt_template.xlsx
+++ b/data/mgmt_template.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="코드마스터" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="조치검증" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판정대장" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="처분대장" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1389,4 +1390,284 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E4A7A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>처분ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>대상ID</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>처분</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>사유</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>기한</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>오너</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>합의</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>DSP-01</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>ERR-002</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>carry-over</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>재발 원인 규명 중 — 운영 초기 집중 모니터링 조건부 이관</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>양희두</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>이관심의 상정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>DSP-02</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>ERR-001</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>종결예정</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>무발생 검증 진행 중 — 심의 전 종결 예상</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>김현일</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>DSP-03</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>ERR-005</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>waiver</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>경미·자가복구 — 위험수용, 월간 모니터링 조건</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>박영희</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>합의완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr"/>
+      <c r="B6" s="8" t="inlineStr"/>
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr"/>
+      <c r="E7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr"/>
+      <c r="B8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="8" t="inlineStr"/>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="7" t="inlineStr"/>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="8" t="inlineStr"/>
+      <c r="F10" s="8" t="inlineStr"/>
+      <c r="G10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="inlineStr"/>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr"/>
+      <c r="D11" s="7" t="inlineStr"/>
+      <c r="E11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr"/>
+      <c r="B12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="8" t="inlineStr"/>
+      <c r="F12" s="8" t="inlineStr"/>
+      <c r="G12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="inlineStr"/>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="7" t="inlineStr"/>
+      <c r="D13" s="7" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="inlineStr"/>
+      <c r="B14" s="8" t="inlineStr"/>
+      <c r="C14" s="8" t="inlineStr"/>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="7" t="inlineStr"/>
+      <c r="B15" s="7" t="inlineStr"/>
+      <c r="C15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="inlineStr"/>
+      <c r="B16" s="8" t="inlineStr"/>
+      <c r="C16" s="8" t="inlineStr"/>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>